--- a/output/daily_ratings/uk_ratings_2026-05-26.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-05-26.xlsx
@@ -524,11 +524,11 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Danehill Star (IRE)</t>
+          <t>Rating (IRE)</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -538,20 +538,22 @@
         <v>132</v>
       </c>
       <c r="K2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>100.16</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>65.59999999999999</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -580,28 +582,30 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rating (IRE)</t>
+          <t>Nammos</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K3" t="n">
-        <v>62</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M3" t="n">
         <v>100.16</v>
       </c>
       <c r="N3" t="n">
-        <v>68.7</v>
+        <v>58.2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -609,7 +613,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -638,30 +642,30 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nammos</t>
+          <t>Bownder (IRE)</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K4" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>100.16</v>
       </c>
       <c r="N4" t="n">
-        <v>60.7</v>
+        <v>64.3</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -669,7 +673,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -698,38 +702,38 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bownder (IRE)</t>
+          <t>The Dark Baron (IRE)</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>24.25</v>
       </c>
       <c r="M5" t="n">
         <v>100.16</v>
       </c>
       <c r="N5" t="n">
-        <v>66.8</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -757,40 +761,24 @@
       <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The Dark Baron (IRE)</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>137</v>
-      </c>
-      <c r="K6" t="n">
-        <v>64</v>
-      </c>
-      <c r="L6" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="M6" t="n">
-        <v>100.16</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20</v>
-      </c>
+          <t>Danehill Star (IRE)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -818,11 +806,11 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Happy Humpo</t>
+          <t>Acclamation Star</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -838,14 +826,16 @@
       <c r="M7" t="n">
         <v>70.26000000000001</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>70.59999999999999</v>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -874,11 +864,11 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Eabha (IRE)</t>
+          <t>Arabica Queen</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -890,18 +880,22 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>3.5</v>
+      </c>
       <c r="M8" t="n">
         <v>70.26000000000001</v>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>65.3</v>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -930,34 +924,38 @@
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Martha Brown</t>
+          <t>Sable Island</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
       <c r="M9" t="n">
         <v>70.26000000000001</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>60.8</v>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -986,28 +984,30 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Acclamation Star</t>
+          <t>Yahaira (IRE)</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
       <c r="M10" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>70.59999999999999</v>
+        <v>54.1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1044,11 +1044,11 @@
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Arabica Queen</t>
+          <t>Nasserein (IRE)</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1061,13 +1061,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3.5</v>
+        <v>6.05</v>
       </c>
       <c r="M11" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>65.3</v>
+        <v>50.1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1104,11 +1104,11 @@
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sable Island</t>
+          <t>Snow On The Beach</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1121,13 +1121,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>7.55</v>
       </c>
       <c r="M12" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>60.8</v>
+        <v>46.1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,11 +1164,11 @@
         <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Yahaira (IRE)</t>
+          <t>Agnes Hathaway</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1181,13 +1181,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>7.58</v>
       </c>
       <c r="M13" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>54.1</v>
+        <v>45.1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1224,11 +1224,11 @@
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nasserein (IRE)</t>
+          <t>Cydney Sweenie</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>6.05</v>
+        <v>11.33</v>
       </c>
       <c r="M14" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>50.1</v>
+        <v>32.7</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1284,11 +1284,11 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Snow On The Beach</t>
+          <t>Ennerdale Water</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1301,13 +1301,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7.55</v>
+        <v>12.08</v>
       </c>
       <c r="M15" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>46.1</v>
+        <v>30.8</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1343,40 +1343,24 @@
       <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
-        <v>7</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Agnes Hathaway</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>128</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="M16" t="n">
-        <v>70.26000000000001</v>
-      </c>
-      <c r="N16" t="n">
-        <v>45.1</v>
-      </c>
+          <t>Martha Brown</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1403,40 +1387,24 @@
       <c r="F17" t="n">
         <v>5</v>
       </c>
-      <c r="G17" t="n">
-        <v>8</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Cydney Sweenie</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>128</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="M17" t="n">
-        <v>70.26000000000001</v>
-      </c>
-      <c r="N17" t="n">
-        <v>32.7</v>
-      </c>
+          <t>Happy Humpo</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1463,40 +1431,24 @@
       <c r="F18" t="n">
         <v>5</v>
       </c>
-      <c r="G18" t="n">
-        <v>9</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ennerdale Water</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>128</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="M18" t="n">
-        <v>70.26000000000001</v>
-      </c>
-      <c r="N18" t="n">
-        <v>30.8</v>
-      </c>
+          <t>Eabha (IRE)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1773,7 +1725,7 @@
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K23" t="n">
         <v>74</v>
@@ -1785,7 +1737,7 @@
         <v>69.45999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>48.2</v>
+        <v>43.6</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1822,34 +1774,36 @@
         <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Danger Alert</t>
+          <t>Aces Wild (IRE)</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K24" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>60.96</v>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1878,28 +1832,30 @@
         <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Aces Wild (IRE)</t>
+          <t>Correspondence</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K25" t="n">
-        <v>70</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M25" t="n">
         <v>60.96</v>
       </c>
       <c r="N25" t="n">
-        <v>72.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1936,30 +1892,30 @@
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Correspondence</t>
+          <t>Level Up (IRE)</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K26" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L26" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
         <v>60.96</v>
       </c>
       <c r="N26" t="n">
-        <v>67.8</v>
+        <v>58.4</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1996,30 +1952,30 @@
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Level Up (IRE)</t>
+          <t>Candy Warhol (USA)</t>
         </is>
       </c>
       <c r="I27" t="n">
         <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K27" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L27" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="M27" t="n">
         <v>60.96</v>
       </c>
       <c r="N27" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2027,7 +1983,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28">
@@ -2056,30 +2012,30 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Candy Warhol (USA)</t>
+          <t>Over Spiced</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K28" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L28" t="n">
-        <v>1.75</v>
+        <v>3.75</v>
       </c>
       <c r="M28" t="n">
         <v>60.96</v>
       </c>
       <c r="N28" t="n">
-        <v>55.1</v>
+        <v>53.5</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2087,7 +2043,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2116,30 +2072,30 @@
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Over Spiced</t>
+          <t>Diomed Spirit</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="K29" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="L29" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="M29" t="n">
         <v>60.96</v>
       </c>
       <c r="N29" t="n">
-        <v>57.6</v>
+        <v>44.1</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2147,7 +2103,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2175,40 +2131,24 @@
       <c r="F30" t="n">
         <v>5</v>
       </c>
-      <c r="G30" t="n">
-        <v>6</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Diomed Spirit</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>121</v>
-      </c>
-      <c r="K30" t="n">
-        <v>56</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="M30" t="n">
-        <v>60.96</v>
-      </c>
-      <c r="N30" t="n">
-        <v>44.1</v>
-      </c>
+          <t>Danger Alert</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2365,7 +2305,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K33" t="n">
         <v>50</v>
@@ -2377,7 +2317,7 @@
         <v>127.37</v>
       </c>
       <c r="N33" t="n">
-        <v>57.8</v>
+        <v>57.3</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2385,7 +2325,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>-3.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="34">
@@ -2425,7 +2365,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="K34" t="n">
         <v>53</v>
@@ -2437,7 +2377,7 @@
         <v>127.37</v>
       </c>
       <c r="N34" t="n">
-        <v>59.2</v>
+        <v>55.9</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2445,7 +2385,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="35">
@@ -2605,7 +2545,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K37" t="n">
         <v>58</v>
@@ -2617,7 +2557,7 @@
         <v>127.37</v>
       </c>
       <c r="N37" t="n">
-        <v>57.8</v>
+        <v>53.5</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2625,7 +2565,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2665,7 +2605,7 @@
         <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K38" t="n">
         <v>49</v>
@@ -2677,7 +2617,7 @@
         <v>127.37</v>
       </c>
       <c r="N38" t="n">
-        <v>43.6</v>
+        <v>40.7</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2725,7 +2665,7 @@
         <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K39" t="n">
         <v>51</v>
@@ -2737,7 +2677,7 @@
         <v>127.37</v>
       </c>
       <c r="N39" t="n">
-        <v>43.2</v>
+        <v>39.9</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2774,34 +2714,36 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Legacy Rock (IRE)</t>
+          <t>Station Bar</t>
         </is>
       </c>
       <c r="I40" t="n">
         <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K40" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>99.42</v>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>78.8</v>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2830,28 +2772,30 @@
         <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Station Bar</t>
+          <t>Mohmentous</t>
         </is>
       </c>
       <c r="I41" t="n">
         <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K41" t="n">
-        <v>62</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
       <c r="M41" t="n">
         <v>99.42</v>
       </c>
       <c r="N41" t="n">
-        <v>78.8</v>
+        <v>73</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2888,11 +2832,11 @@
         <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Mohmentous</t>
+          <t>Phantom Shadow (FR)</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2905,13 +2849,13 @@
         <v>59</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="M42" t="n">
         <v>99.42</v>
       </c>
       <c r="N42" t="n">
-        <v>73</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2947,40 +2891,24 @@
       <c r="F43" t="n">
         <v>6</v>
       </c>
-      <c r="G43" t="n">
-        <v>3</v>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Phantom Shadow (FR)</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>3</v>
-      </c>
-      <c r="J43" t="n">
-        <v>129</v>
-      </c>
-      <c r="K43" t="n">
-        <v>59</v>
-      </c>
-      <c r="L43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="M43" t="n">
-        <v>99.42</v>
-      </c>
-      <c r="N43" t="n">
-        <v>67.90000000000001</v>
-      </c>
+          <t>Legacy Rock (IRE)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3006,34 +2934,36 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Albion Power (IRE)</t>
+          <t>The Liffey (IRE)</t>
         </is>
       </c>
       <c r="I44" t="n">
         <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K44" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>101.26</v>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>44.2</v>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3060,28 +2990,30 @@
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>The Liffey (IRE)</t>
+          <t>Battle Borne (IRE)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="K45" t="n">
-        <v>85</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3.5</v>
+      </c>
       <c r="M45" t="n">
         <v>101.26</v>
       </c>
       <c r="N45" t="n">
-        <v>44.2</v>
+        <v>26.2</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3089,7 +3021,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="46">
@@ -3116,30 +3048,30 @@
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Battle Borne (IRE)</t>
+          <t>Land Of The Giants (IRE)</t>
         </is>
       </c>
       <c r="I46" t="n">
         <v>4</v>
       </c>
       <c r="J46" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K46" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L46" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M46" t="n">
         <v>101.26</v>
       </c>
       <c r="N46" t="n">
-        <v>32.8</v>
+        <v>30.9</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3147,7 +3079,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3174,30 +3106,30 @@
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Land Of The Giants (IRE)</t>
+          <t>Wolfpack</t>
         </is>
       </c>
       <c r="I47" t="n">
         <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K47" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L47" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="M47" t="n">
         <v>101.26</v>
       </c>
       <c r="N47" t="n">
-        <v>30.9</v>
+        <v>20.1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3205,7 +3137,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="48">
@@ -3232,30 +3164,30 @@
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Wolfpack</t>
+          <t>Independent Expert (IRE)</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="K48" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L48" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="M48" t="n">
         <v>101.26</v>
       </c>
       <c r="N48" t="n">
-        <v>24.9</v>
+        <v>32</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3263,7 +3195,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3290,30 +3222,30 @@
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Independent Expert (IRE)</t>
+          <t>Imperial Fighter (IRE)</t>
         </is>
       </c>
       <c r="I49" t="n">
         <v>7</v>
       </c>
       <c r="J49" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="K49" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="L49" t="n">
-        <v>5.4</v>
+        <v>6.9</v>
       </c>
       <c r="M49" t="n">
         <v>101.26</v>
       </c>
       <c r="N49" t="n">
-        <v>32</v>
+        <v>20.6</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3321,7 +3253,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50">
@@ -3348,30 +3280,30 @@
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Imperial Fighter (IRE)</t>
+          <t>Cosmic Force</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K50" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="L50" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="M50" t="n">
         <v>101.26</v>
       </c>
       <c r="N50" t="n">
-        <v>20.6</v>
+        <v>22.9</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3379,7 +3311,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3406,30 +3338,30 @@
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Cosmic Force</t>
+          <t>North Ocean (IRE)</t>
         </is>
       </c>
       <c r="I51" t="n">
         <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K51" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>7.4</v>
+        <v>7.55</v>
       </c>
       <c r="M51" t="n">
         <v>101.26</v>
       </c>
       <c r="N51" t="n">
-        <v>22.9</v>
+        <v>28</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3437,7 +3369,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3464,30 +3396,30 @@
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>North Ocean (IRE)</t>
+          <t>Ledger (IRE)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L52" t="n">
-        <v>7.55</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M52" t="n">
         <v>101.26</v>
       </c>
       <c r="N52" t="n">
-        <v>32.9</v>
+        <v>17.2</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3495,7 +3427,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3522,30 +3454,30 @@
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Ledger (IRE)</t>
+          <t>Yosemite Gold</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="K53" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="L53" t="n">
-        <v>9.300000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="M53" t="n">
         <v>101.26</v>
       </c>
       <c r="N53" t="n">
-        <v>20.2</v>
+        <v>12.8</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3579,40 +3511,24 @@
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
-        <v>10</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Yosemite Gold</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>5</v>
-      </c>
-      <c r="J54" t="n">
-        <v>142</v>
-      </c>
-      <c r="K54" t="n">
-        <v>69</v>
-      </c>
-      <c r="L54" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M54" t="n">
-        <v>101.26</v>
-      </c>
-      <c r="N54" t="n">
-        <v>15.7</v>
-      </c>
+          <t>Albion Power (IRE)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3638,11 +3554,11 @@
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Fates Gambit (IRE)</t>
+          <t>Jamestown (IRE)</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3652,20 +3568,22 @@
         <v>134</v>
       </c>
       <c r="K55" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
         <v>86.20999999999999</v>
       </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>76.90000000000001</v>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3692,28 +3610,30 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Jamestown (IRE)</t>
+          <t>Nautic Star (IRE)</t>
         </is>
       </c>
       <c r="I56" t="n">
         <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K56" t="n">
-        <v>84</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>8</v>
+      </c>
       <c r="M56" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>76.90000000000001</v>
+        <v>46.5</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3748,30 +3668,30 @@
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nautic Star (IRE)</t>
+          <t>Ribble Emperor (IRE)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L57" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M57" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3779,7 +3699,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3806,30 +3726,30 @@
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Ribble Emperor (IRE)</t>
+          <t>Rayzera (IRE)</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="K58" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="L58" t="n">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="M58" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>52.2</v>
+        <v>42.2</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3837,7 +3757,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3864,30 +3784,30 @@
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Rayzera (IRE)</t>
+          <t>Henry Hudson</t>
         </is>
       </c>
       <c r="I59" t="n">
         <v>3</v>
       </c>
       <c r="J59" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K59" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>9.75</v>
+        <v>13.25</v>
       </c>
       <c r="M59" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>42.2</v>
+        <v>37.1</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3922,30 +3842,30 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Henry Hudson</t>
+          <t>Make The Tide (IRE)</t>
         </is>
       </c>
       <c r="I60" t="n">
         <v>3</v>
       </c>
       <c r="J60" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>13.25</v>
+        <v>13.35</v>
       </c>
       <c r="M60" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>37.1</v>
+        <v>31.8</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -3953,7 +3873,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="61">
@@ -3980,11 +3900,11 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Make The Tide (IRE)</t>
+          <t>Kirkland Sioux (IRE)</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -3997,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>13.35</v>
+        <v>13.45</v>
       </c>
       <c r="M61" t="n">
         <v>86.20999999999999</v>
@@ -4011,7 +3931,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
@@ -4038,30 +3958,30 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kirkland Sioux (IRE)</t>
+          <t>Unidos</t>
         </is>
       </c>
       <c r="I62" t="n">
         <v>3</v>
       </c>
       <c r="J62" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>13.45</v>
+        <v>15.2</v>
       </c>
       <c r="M62" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>31.8</v>
+        <v>30.6</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4069,7 +3989,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4096,30 +4016,30 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Unidos</t>
+          <t>Gilts (IRE)</t>
         </is>
       </c>
       <c r="I63" t="n">
         <v>3</v>
       </c>
       <c r="J63" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>15.2</v>
+        <v>17.95</v>
       </c>
       <c r="M63" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>30.6</v>
+        <v>16.8</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4154,11 +4074,11 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Gilts (IRE)</t>
+          <t>Themis (IRE)</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4171,13 +4091,13 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>17.95</v>
+        <v>19.95</v>
       </c>
       <c r="M64" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>19.9</v>
+        <v>13.4</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4212,11 +4132,11 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Themis (IRE)</t>
+          <t>Miss Mercier (IRE)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4229,17 +4149,17 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>19.95</v>
+        <v>28.45</v>
       </c>
       <c r="M65" t="n">
         <v>86.20999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>13.4</v>
+        <v>3.6</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -4269,40 +4189,24 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="n">
-        <v>11</v>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Miss Mercier (IRE)</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" t="n">
-        <v>129</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>28.45</v>
-      </c>
-      <c r="M66" t="n">
-        <v>86.20999999999999</v>
-      </c>
-      <c r="N66" t="n">
-        <v>3.6</v>
-      </c>
+          <t>Fates Gambit (IRE)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4328,18 +4232,18 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Allirelandmaterial (IRE)</t>
+          <t>Lamar Canyon (IRE)</t>
         </is>
       </c>
       <c r="I67" t="n">
         <v>3</v>
       </c>
       <c r="J67" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -4348,14 +4252,16 @@
       <c r="M67" t="n">
         <v>60.09</v>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>64.7</v>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4382,28 +4288,30 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Lamar Canyon (IRE)</t>
+          <t>Focaccia (IRE)</t>
         </is>
       </c>
       <c r="I68" t="n">
         <v>3</v>
       </c>
       <c r="J68" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M68" t="n">
         <v>60.09</v>
       </c>
       <c r="N68" t="n">
-        <v>70.40000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4411,7 +4319,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
@@ -4438,30 +4346,30 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Focaccia (IRE)</t>
+          <t>Cool Azul (IRE)</t>
         </is>
       </c>
       <c r="I69" t="n">
         <v>3</v>
       </c>
       <c r="J69" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M69" t="n">
         <v>60.09</v>
       </c>
       <c r="N69" t="n">
-        <v>62.7</v>
+        <v>63.5</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4469,7 +4377,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4496,11 +4404,11 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Cool Azul (IRE)</t>
+          <t>Sparky Sparky (IRE)</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4513,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="M70" t="n">
         <v>60.09</v>
       </c>
       <c r="N70" t="n">
-        <v>63.5</v>
+        <v>58.9</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4527,7 +4435,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71">
@@ -4554,30 +4462,30 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sparky Sparky (IRE)</t>
+          <t>Beach Barbie (IRE)</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M71" t="n">
         <v>60.09</v>
       </c>
       <c r="N71" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4612,30 +4520,30 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Beach Barbie (IRE)</t>
+          <t>Banshof (IRE)</t>
         </is>
       </c>
       <c r="I72" t="n">
         <v>4</v>
       </c>
       <c r="J72" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="M72" t="n">
         <v>60.09</v>
       </c>
       <c r="N72" t="n">
-        <v>58.8</v>
+        <v>62</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4643,7 +4551,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4670,30 +4578,30 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banshof (IRE)</t>
+          <t>Aughlish (IRE)</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L73" t="n">
-        <v>3.53</v>
+        <v>5.28</v>
       </c>
       <c r="M73" t="n">
         <v>60.09</v>
       </c>
       <c r="N73" t="n">
-        <v>62</v>
+        <v>43.8</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4701,7 +4609,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="74">
@@ -4728,30 +4636,30 @@
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Aughlish (IRE)</t>
+          <t>Reposado</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="K74" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L74" t="n">
-        <v>5.28</v>
+        <v>7.529999999999999</v>
       </c>
       <c r="M74" t="n">
         <v>60.09</v>
       </c>
       <c r="N74" t="n">
-        <v>43.8</v>
+        <v>46.8</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4759,7 +4667,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4786,30 +4694,30 @@
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Reposado</t>
+          <t>Auguste Gusteau (IRE)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="K75" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>7.53</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M75" t="n">
         <v>60.09</v>
       </c>
       <c r="N75" t="n">
-        <v>46.8</v>
+        <v>28.5</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -4817,7 +4725,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4843,40 +4751,24 @@
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="n">
-        <v>9</v>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Auguste Gusteau (IRE)</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" t="n">
-        <v>134</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>9.780000000000001</v>
-      </c>
-      <c r="M76" t="n">
-        <v>60.09</v>
-      </c>
-      <c r="N76" t="n">
-        <v>33.4</v>
-      </c>
+          <t>Allirelandmaterial (IRE)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4902,34 +4794,36 @@
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Real Encounter (IRE)</t>
+          <t>Cuban Grey</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J77" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K77" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
         <v>59.78</v>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>74.90000000000001</v>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="78">
@@ -4956,28 +4850,30 @@
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Cuban Grey</t>
+          <t>Collective Power (IRE)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J78" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K78" t="n">
-        <v>75</v>
-      </c>
-      <c r="L78" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M78" t="n">
         <v>59.78</v>
       </c>
       <c r="N78" t="n">
-        <v>74.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -4985,7 +4881,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -5012,30 +4908,30 @@
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Collective Power (IRE)</t>
+          <t>All The Girls (IRE)</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K79" t="n">
         <v>79</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="M79" t="n">
         <v>59.78</v>
       </c>
       <c r="N79" t="n">
-        <v>76</v>
+        <v>63.3</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5043,7 +4939,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5070,30 +4966,30 @@
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>All The Girls (IRE)</t>
+          <t>Sovereign Cry (IRE)</t>
         </is>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K80" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
         <v>59.78</v>
       </c>
       <c r="N80" t="n">
-        <v>63.3</v>
+        <v>53.6</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5128,30 +5024,30 @@
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sovereign Cry (IRE)</t>
+          <t>Clonmacash</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K81" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L81" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="M81" t="n">
         <v>59.78</v>
       </c>
       <c r="N81" t="n">
-        <v>59.7</v>
+        <v>51.7</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5159,7 +5055,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="82">
@@ -5186,11 +5082,11 @@
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Clonmacash</t>
+          <t>Buddy Batt (IRE)</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5203,13 +5099,13 @@
         <v>80</v>
       </c>
       <c r="L82" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="M82" t="n">
         <v>59.78</v>
       </c>
       <c r="N82" t="n">
-        <v>58</v>
+        <v>52.6</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5217,7 +5113,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5244,30 +5140,30 @@
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Buddy Batt (IRE)</t>
+          <t>Harrys Hill</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J83" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K83" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L83" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="M83" t="n">
         <v>59.78</v>
       </c>
       <c r="N83" t="n">
-        <v>52.6</v>
+        <v>44.2</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5275,7 +5171,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
@@ -5302,30 +5198,30 @@
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Harrys Hill</t>
+          <t>Billboa</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J84" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K84" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="L84" t="n">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="M84" t="n">
         <v>59.78</v>
       </c>
       <c r="N84" t="n">
-        <v>47.7</v>
+        <v>36.5</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5333,7 +5229,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="85">
@@ -5360,30 +5256,30 @@
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Billboa</t>
+          <t>Arctic Steps (IRE)</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K85" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L85" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M85" t="n">
         <v>59.78</v>
       </c>
       <c r="N85" t="n">
-        <v>36.5</v>
+        <v>40.3</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5391,7 +5287,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5418,11 +5314,11 @@
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Arctic Steps (IRE)</t>
+          <t>Lethimfly (IRE)</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5435,13 +5331,13 @@
         <v>74</v>
       </c>
       <c r="L86" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M86" t="n">
         <v>59.78</v>
       </c>
       <c r="N86" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5449,7 +5345,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -5476,30 +5372,30 @@
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
+        <v>11</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Jered Maddox</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
         <v>10</v>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Lethimfly (IRE)</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>4</v>
-      </c>
       <c r="J87" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="K87" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="L87" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="M87" t="n">
         <v>59.78</v>
       </c>
       <c r="N87" t="n">
-        <v>45.2</v>
+        <v>28.8</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -5507,7 +5403,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5534,30 +5430,30 @@
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Jered Maddox</t>
+          <t>Sporting Hero</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J88" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K88" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="L88" t="n">
-        <v>8.1</v>
+        <v>11.6</v>
       </c>
       <c r="M88" t="n">
         <v>59.78</v>
       </c>
       <c r="N88" t="n">
-        <v>28.8</v>
+        <v>26.9</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -5565,7 +5461,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5591,40 +5487,24 @@
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="n">
-        <v>12</v>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sporting Hero</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>6</v>
-      </c>
-      <c r="J89" t="n">
-        <v>138</v>
-      </c>
-      <c r="K89" t="n">
-        <v>78</v>
-      </c>
-      <c r="L89" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M89" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="N89" t="n">
-        <v>31.7</v>
-      </c>
+          <t>Real Encounter (IRE)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P89" t="n">
-        <v>1</v>
-      </c>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5650,18 +5530,18 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Diligo (IRE)</t>
+          <t>Believed (IRE)</t>
         </is>
       </c>
       <c r="I90" t="n">
         <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -5670,14 +5550,16 @@
       <c r="M90" t="n">
         <v>154.95</v>
       </c>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>58</v>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5704,11 +5586,11 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Believed (IRE)</t>
+          <t>Cite Florale (FR)</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5720,12 +5602,14 @@
       <c r="K91" t="n">
         <v>0</v>
       </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>8.5</v>
+      </c>
       <c r="M91" t="n">
         <v>154.95</v>
       </c>
       <c r="N91" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -5733,7 +5617,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="92">
@@ -5760,30 +5644,30 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Cite Florale (FR)</t>
+          <t>Police Gazette (USA)</t>
         </is>
       </c>
       <c r="I92" t="n">
         <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="M92" t="n">
         <v>154.95</v>
       </c>
       <c r="N92" t="n">
-        <v>42</v>
+        <v>46.9</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -5791,7 +5675,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5818,11 +5702,11 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Police Gazette (USA)</t>
+          <t>Teoest (IRE)</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -5835,13 +5719,13 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="M93" t="n">
         <v>154.95</v>
       </c>
       <c r="N93" t="n">
-        <v>46.9</v>
+        <v>44.2</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -5876,11 +5760,11 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Teoest (IRE)</t>
+          <t>Minella Rockett (IRE)</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -5890,16 +5774,16 @@
         <v>134</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L94" t="n">
-        <v>10.25</v>
+        <v>10.75</v>
       </c>
       <c r="M94" t="n">
         <v>154.95</v>
       </c>
       <c r="N94" t="n">
-        <v>44.2</v>
+        <v>42.7</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -5907,7 +5791,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5934,11 +5818,11 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Minella Rockett (IRE)</t>
+          <t>Yogini (IRE)</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -5948,16 +5832,16 @@
         <v>134</v>
       </c>
       <c r="K95" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>10.75</v>
+        <v>10.8</v>
       </c>
       <c r="M95" t="n">
         <v>154.95</v>
       </c>
       <c r="N95" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -5965,7 +5849,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -5992,30 +5876,30 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Yogini (IRE)</t>
+          <t>Werifesteria (USA)</t>
         </is>
       </c>
       <c r="I96" t="n">
         <v>3</v>
       </c>
       <c r="J96" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>10.8</v>
+        <v>13.05</v>
       </c>
       <c r="M96" t="n">
         <v>154.95</v>
       </c>
       <c r="N96" t="n">
-        <v>43</v>
+        <v>33.8</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6023,7 +5907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -6050,30 +5934,30 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Werifesteria (USA)</t>
+          <t>Tanzanite Diamond (IRE)</t>
         </is>
       </c>
       <c r="I97" t="n">
         <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>13.05</v>
+        <v>17.55</v>
       </c>
       <c r="M97" t="n">
         <v>154.95</v>
       </c>
       <c r="N97" t="n">
-        <v>33.8</v>
+        <v>30.4</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6108,11 +5992,11 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tanzanite Diamond (IRE)</t>
+          <t>Avoca Woods</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -6125,17 +6009,17 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>17.55</v>
+        <v>24.55</v>
       </c>
       <c r="M98" t="n">
         <v>154.95</v>
       </c>
       <c r="N98" t="n">
-        <v>30.4</v>
+        <v>27.8</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -6166,30 +6050,30 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Avoca Woods</t>
+          <t>Nosmokewithoutfire (IRE)</t>
         </is>
       </c>
       <c r="I99" t="n">
         <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>24.55</v>
+        <v>32.05</v>
       </c>
       <c r="M99" t="n">
         <v>154.95</v>
       </c>
       <c r="N99" t="n">
-        <v>27.8</v>
+        <v>13.3</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6223,40 +6107,24 @@
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="n">
-        <v>10</v>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Nosmokewithoutfire (IRE)</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>3</v>
-      </c>
-      <c r="J100" t="n">
-        <v>134</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="M100" t="n">
-        <v>154.95</v>
-      </c>
-      <c r="N100" t="n">
-        <v>18.9</v>
-      </c>
+          <t>Diligo (IRE)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6282,34 +6150,36 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Eastern Wind</t>
+          <t>Grey Fable (IRE)</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J101" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K101" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
         <v>156.79</v>
       </c>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>41.4</v>
+      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>-14.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="102">
@@ -6336,34 +6206,38 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tara Power (IRE)</t>
+          <t>Copper Craft (IRE)</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K102" t="n">
-        <v>37</v>
-      </c>
-      <c r="L102" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M102" t="n">
         <v>156.79</v>
       </c>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>34.8</v>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-14.5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="103">
@@ -6390,28 +6264,30 @@
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Grey Fable (IRE)</t>
+          <t>Chopsticks (IRE)</t>
         </is>
       </c>
       <c r="I103" t="n">
         <v>6</v>
       </c>
       <c r="J103" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K103" t="n">
-        <v>56</v>
-      </c>
-      <c r="L103" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.65</v>
+      </c>
       <c r="M103" t="n">
         <v>156.79</v>
       </c>
       <c r="N103" t="n">
-        <v>41.4</v>
+        <v>46.6</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -6419,7 +6295,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -6446,30 +6322,30 @@
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Copper Craft (IRE)</t>
+          <t>Highway Sixty One (IRE)</t>
         </is>
       </c>
       <c r="I104" t="n">
         <v>4</v>
       </c>
       <c r="J104" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K104" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L104" t="n">
-        <v>0.15</v>
+        <v>2.9</v>
       </c>
       <c r="M104" t="n">
         <v>156.79</v>
       </c>
       <c r="N104" t="n">
-        <v>34.8</v>
+        <v>23.9</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -6477,7 +6353,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="105">
@@ -6504,30 +6380,30 @@
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Chopsticks (IRE)</t>
+          <t>Folk Warrior (IRE)</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="K105" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L105" t="n">
-        <v>0.65</v>
+        <v>3.05</v>
       </c>
       <c r="M105" t="n">
         <v>156.79</v>
       </c>
       <c r="N105" t="n">
-        <v>46.6</v>
+        <v>31.3</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -6535,7 +6411,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="106">
@@ -6562,30 +6438,30 @@
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Highway Sixty One (IRE)</t>
+          <t>Jawhary</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J106" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="K106" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="L106" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="M106" t="n">
         <v>156.79</v>
       </c>
       <c r="N106" t="n">
-        <v>28.2</v>
+        <v>42.2</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -6593,7 +6469,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
@@ -6620,30 +6496,30 @@
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Folk Warrior (IRE)</t>
+          <t>Numidia (IRE)</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J107" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K107" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="L107" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="M107" t="n">
         <v>156.79</v>
       </c>
       <c r="N107" t="n">
-        <v>31.3</v>
+        <v>37.3</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -6651,7 +6527,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -6678,30 +6554,30 @@
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Jawhary</t>
+          <t>Smooth</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="K108" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L108" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="M108" t="n">
         <v>156.79</v>
       </c>
       <c r="N108" t="n">
-        <v>42.2</v>
+        <v>14.5</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -6709,7 +6585,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="109">
@@ -6736,30 +6612,30 @@
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Numidia (IRE)</t>
+          <t>Church Mountain (IRE)</t>
         </is>
       </c>
       <c r="I109" t="n">
         <v>8</v>
       </c>
       <c r="J109" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K109" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L109" t="n">
-        <v>3.65</v>
+        <v>10.15</v>
       </c>
       <c r="M109" t="n">
         <v>156.79</v>
       </c>
       <c r="N109" t="n">
-        <v>37.3</v>
+        <v>26.8</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -6767,7 +6643,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -6794,30 +6670,30 @@
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Smooth</t>
+          <t>Sarmiento Power (IRE)</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K110" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L110" t="n">
-        <v>8.4</v>
+        <v>13.15</v>
       </c>
       <c r="M110" t="n">
         <v>156.79</v>
       </c>
       <c r="N110" t="n">
-        <v>18.8</v>
+        <v>15.4</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -6825,7 +6701,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -6852,38 +6728,38 @@
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Church Mountain (IRE)</t>
+          <t>Angel Harry (FR)</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="K111" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="L111" t="n">
-        <v>10.15</v>
+        <v>27.15</v>
       </c>
       <c r="M111" t="n">
         <v>156.79</v>
       </c>
       <c r="N111" t="n">
-        <v>26.8</v>
+        <v>-12.6</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112">
@@ -6910,38 +6786,38 @@
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Sarmiento Power (IRE)</t>
+          <t>Kilgharrahs Love (IRE)</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="K112" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L112" t="n">
-        <v>13.15</v>
+        <v>27.3</v>
       </c>
       <c r="M112" t="n">
         <v>156.79</v>
       </c>
       <c r="N112" t="n">
-        <v>15.4</v>
+        <v>-21.9</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="113">
@@ -6968,30 +6844,30 @@
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Angel Harry (FR)</t>
+          <t>Skib Gold</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J113" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K113" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="L113" t="n">
-        <v>27.15</v>
+        <v>28.05</v>
       </c>
       <c r="M113" t="n">
         <v>156.79</v>
       </c>
       <c r="N113" t="n">
-        <v>-12.6</v>
+        <v>-5.5</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -6999,7 +6875,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -7025,40 +6901,24 @@
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="n">
-        <v>12</v>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Kilgharrahs Love (IRE)</t>
-        </is>
-      </c>
-      <c r="I114" t="n">
-        <v>4</v>
-      </c>
-      <c r="J114" t="n">
-        <v>122</v>
-      </c>
-      <c r="K114" t="n">
-        <v>40</v>
-      </c>
-      <c r="L114" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="M114" t="n">
-        <v>156.79</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-21.9</v>
-      </c>
+          <t>Eastern Wind</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P114" t="n">
-        <v>-1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7083,40 +6943,24 @@
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="n">
-        <v>13</v>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Skib Gold</t>
-        </is>
-      </c>
-      <c r="I115" t="n">
-        <v>5</v>
-      </c>
-      <c r="J115" t="n">
-        <v>138</v>
-      </c>
-      <c r="K115" t="n">
-        <v>56</v>
-      </c>
-      <c r="L115" t="n">
-        <v>28.05</v>
-      </c>
-      <c r="M115" t="n">
-        <v>156.79</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1.7</v>
-      </c>
+          <t>Tara Power (IRE)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P115" t="n">
-        <v>2</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7331,7 +7175,7 @@
         <v>82</v>
       </c>
       <c r="L119" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="M119" t="n">
         <v>137.24</v>
@@ -7499,19 +7343,19 @@
         <v>4</v>
       </c>
       <c r="J122" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K122" t="n">
         <v>75</v>
       </c>
       <c r="L122" t="n">
-        <v>6.43</v>
+        <v>6.430000000000001</v>
       </c>
       <c r="M122" t="n">
         <v>137.24</v>
       </c>
       <c r="N122" t="n">
-        <v>43.3</v>
+        <v>40.4</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -7563,7 +7407,7 @@
         <v>68</v>
       </c>
       <c r="L123" t="n">
-        <v>7.68</v>
+        <v>7.680000000000001</v>
       </c>
       <c r="M123" t="n">
         <v>137.24</v>
@@ -7615,7 +7459,7 @@
         <v>4</v>
       </c>
       <c r="J124" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -7627,7 +7471,7 @@
         <v>137.24</v>
       </c>
       <c r="N124" t="n">
-        <v>38.7</v>
+        <v>32.6</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -7731,7 +7575,7 @@
         <v>4</v>
       </c>
       <c r="J126" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -7743,7 +7587,7 @@
         <v>137.24</v>
       </c>
       <c r="N126" t="n">
-        <v>27.7</v>
+        <v>21.6</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -7838,18 +7682,18 @@
         <v>4</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Rattenbury (IRE)</t>
+          <t>Libertango (IRE)</t>
         </is>
       </c>
       <c r="I128" t="n">
         <v>2</v>
       </c>
       <c r="J128" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -7858,14 +7702,16 @@
       <c r="M128" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" t="n">
+        <v>77.5</v>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -7894,11 +7740,11 @@
         <v>4</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Shoof</t>
+          <t>Savage Mariner (IRE)</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -7910,18 +7756,22 @@
       <c r="K129" t="n">
         <v>0</v>
       </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="L129" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M129" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" t="n">
+        <v>75.3</v>
+      </c>
       <c r="O129" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -7950,11 +7800,11 @@
         <v>4</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>High Calibre</t>
+          <t>Captaincy (IRE)</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -7966,18 +7816,22 @@
       <c r="K130" t="n">
         <v>0</v>
       </c>
-      <c r="L130" t="inlineStr"/>
+      <c r="L130" t="n">
+        <v>4.5</v>
+      </c>
       <c r="M130" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="n">
+        <v>68.3</v>
+      </c>
       <c r="O130" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -8006,28 +7860,30 @@
         <v>4</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Libertango (IRE)</t>
+          <t>Victory Gold (IRE)</t>
         </is>
       </c>
       <c r="I131" t="n">
         <v>2</v>
       </c>
       <c r="J131" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
       </c>
-      <c r="L131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M131" t="n">
         <v>70.54000000000001</v>
       </c>
       <c r="N131" t="n">
-        <v>77.5</v>
+        <v>62.1</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -8064,30 +7920,30 @@
         <v>4</v>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Savage Mariner (IRE)</t>
+          <t>Royal Message (IRE)</t>
         </is>
       </c>
       <c r="I132" t="n">
         <v>2</v>
       </c>
       <c r="J132" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="M132" t="n">
         <v>70.54000000000001</v>
       </c>
       <c r="N132" t="n">
-        <v>75.3</v>
+        <v>53.2</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -8124,11 +7980,11 @@
         <v>4</v>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Captaincy (IRE)</t>
+          <t>Valdoro (IRE)</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -8141,13 +7997,13 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>4.5</v>
+        <v>9.25</v>
       </c>
       <c r="M133" t="n">
         <v>70.54000000000001</v>
       </c>
       <c r="N133" t="n">
-        <v>68.3</v>
+        <v>52.9</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -8184,11 +8040,11 @@
         <v>4</v>
       </c>
       <c r="G134" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Victory Gold (IRE)</t>
+          <t>Miami To Ibiza</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -8201,13 +8057,13 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="M134" t="n">
         <v>70.54000000000001</v>
       </c>
       <c r="N134" t="n">
-        <v>62.1</v>
+        <v>43.4</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -8244,34 +8100,34 @@
         <v>4</v>
       </c>
       <c r="G135" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Royal Message (IRE)</t>
+          <t>Lion O (IRE)</t>
         </is>
       </c>
       <c r="I135" t="n">
         <v>2</v>
       </c>
       <c r="J135" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>7.5</v>
+        <v>22</v>
       </c>
       <c r="M135" t="n">
         <v>70.54000000000001</v>
       </c>
       <c r="N135" t="n">
-        <v>53.2</v>
+        <v>27.3</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -8303,40 +8159,24 @@
       <c r="F136" t="n">
         <v>4</v>
       </c>
-      <c r="G136" t="n">
-        <v>6</v>
-      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Valdoro (IRE)</t>
-        </is>
-      </c>
-      <c r="I136" t="n">
-        <v>2</v>
-      </c>
-      <c r="J136" t="n">
-        <v>133</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="M136" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="N136" t="n">
-        <v>52.9</v>
-      </c>
+          <t>High Calibre</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8363,40 +8203,24 @@
       <c r="F137" t="n">
         <v>4</v>
       </c>
-      <c r="G137" t="n">
-        <v>7</v>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Miami To Ibiza</t>
-        </is>
-      </c>
-      <c r="I137" t="n">
-        <v>2</v>
-      </c>
-      <c r="J137" t="n">
-        <v>133</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>11</v>
-      </c>
-      <c r="M137" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="N137" t="n">
-        <v>43.4</v>
-      </c>
+          <t>Shoof</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8423,40 +8247,24 @@
       <c r="F138" t="n">
         <v>4</v>
       </c>
-      <c r="G138" t="n">
-        <v>8</v>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Lion O (IRE)</t>
-        </is>
-      </c>
-      <c r="I138" t="n">
-        <v>2</v>
-      </c>
-      <c r="J138" t="n">
-        <v>133</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
-        <v>22</v>
-      </c>
-      <c r="M138" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="N138" t="n">
-        <v>27.3</v>
-      </c>
+          <t>Rattenbury (IRE)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8484,18 +8292,18 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Bluestone Lady (IRE)</t>
+          <t>Abrahamsen (IRE)</t>
         </is>
       </c>
       <c r="I139" t="n">
         <v>2</v>
       </c>
       <c r="J139" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -8504,14 +8312,16 @@
       <c r="M139" t="n">
         <v>85.26000000000001</v>
       </c>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="n">
+        <v>57.7</v>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P139" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -8540,11 +8350,11 @@
         <v>5</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Abrahamsen (IRE)</t>
+          <t>Parading</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -8556,12 +8366,14 @@
       <c r="K140" t="n">
         <v>0</v>
       </c>
-      <c r="L140" t="inlineStr"/>
+      <c r="L140" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M140" t="n">
         <v>85.26000000000001</v>
       </c>
       <c r="N140" t="n">
-        <v>57.7</v>
+        <v>56</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -8598,11 +8410,11 @@
         <v>5</v>
       </c>
       <c r="G141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Parading</t>
+          <t>Jazzy Bay (IRE)</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -8615,13 +8427,13 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="M141" t="n">
         <v>85.26000000000001</v>
       </c>
       <c r="N141" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -8658,11 +8470,11 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Jazzy Bay (IRE)</t>
+          <t>Village Hall</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -8675,13 +8487,13 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>1.25</v>
+        <v>15.25</v>
       </c>
       <c r="M142" t="n">
         <v>85.26000000000001</v>
       </c>
       <c r="N142" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -8718,34 +8530,34 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Village Hall</t>
+          <t>Showmethebubbles</t>
         </is>
       </c>
       <c r="I143" t="n">
         <v>2</v>
       </c>
       <c r="J143" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>15.25</v>
+        <v>42.25</v>
       </c>
       <c r="M143" t="n">
         <v>85.26000000000001</v>
       </c>
       <c r="N143" t="n">
-        <v>5</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -8777,40 +8589,24 @@
       <c r="F144" t="n">
         <v>5</v>
       </c>
-      <c r="G144" t="n">
-        <v>5</v>
-      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Showmethebubbles</t>
-        </is>
-      </c>
-      <c r="I144" t="n">
-        <v>2</v>
-      </c>
-      <c r="J144" t="n">
-        <v>125</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="M144" t="n">
-        <v>85.26000000000001</v>
-      </c>
-      <c r="N144" t="n">
-        <v>-79.90000000000001</v>
-      </c>
+          <t>Bluestone Lady (IRE)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8838,34 +8634,36 @@
         <v>4</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>El Vamos (IRE)</t>
+          <t>Harlequin Breeze (IRE)</t>
         </is>
       </c>
       <c r="I145" t="n">
         <v>3</v>
       </c>
       <c r="J145" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="n">
         <v>102.78</v>
       </c>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="n">
+        <v>72.5</v>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8894,34 +8692,38 @@
         <v>4</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Seet</t>
+          <t>Crownright</t>
         </is>
       </c>
       <c r="I146" t="n">
         <v>3</v>
       </c>
       <c r="J146" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
       </c>
-      <c r="L146" t="inlineStr"/>
+      <c r="L146" t="n">
+        <v>4.5</v>
+      </c>
       <c r="M146" t="n">
         <v>102.78</v>
       </c>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="n">
+        <v>61.8</v>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -8950,11 +8752,11 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Harlequin Breeze (IRE)</t>
+          <t>Molo Del Palazzo (USA)</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -8964,14 +8766,16 @@
         <v>128</v>
       </c>
       <c r="K147" t="n">
-        <v>84</v>
-      </c>
-      <c r="L147" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>6.75</v>
+      </c>
       <c r="M147" t="n">
         <v>102.78</v>
       </c>
       <c r="N147" t="n">
-        <v>72.5</v>
+        <v>55.1</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -9008,30 +8812,30 @@
         <v>4</v>
       </c>
       <c r="G148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Crownright</t>
+          <t>Caim</t>
         </is>
       </c>
       <c r="I148" t="n">
         <v>3</v>
       </c>
       <c r="J148" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="L148" t="n">
-        <v>4.5</v>
+        <v>10.75</v>
       </c>
       <c r="M148" t="n">
         <v>102.78</v>
       </c>
       <c r="N148" t="n">
-        <v>61.8</v>
+        <v>48</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -9067,40 +8871,24 @@
       <c r="F149" t="n">
         <v>4</v>
       </c>
-      <c r="G149" t="n">
-        <v>3</v>
-      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Molo Del Palazzo (USA)</t>
-        </is>
-      </c>
-      <c r="I149" t="n">
-        <v>3</v>
-      </c>
-      <c r="J149" t="n">
-        <v>128</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="M149" t="n">
-        <v>102.78</v>
-      </c>
-      <c r="N149" t="n">
-        <v>55.1</v>
-      </c>
+          <t>Seet</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9127,40 +8915,24 @@
       <c r="F150" t="n">
         <v>4</v>
       </c>
-      <c r="G150" t="n">
-        <v>4</v>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Caim</t>
-        </is>
-      </c>
-      <c r="I150" t="n">
-        <v>3</v>
-      </c>
-      <c r="J150" t="n">
-        <v>133</v>
-      </c>
-      <c r="K150" t="n">
-        <v>91</v>
-      </c>
-      <c r="L150" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="M150" t="n">
-        <v>102.78</v>
-      </c>
-      <c r="N150" t="n">
-        <v>48</v>
-      </c>
+          <t>El Vamos (IRE)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9188,34 +8960,36 @@
         <v>6</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Elashgar (IRE)</t>
+          <t>Escape Magic</t>
         </is>
       </c>
       <c r="I151" t="n">
         <v>3</v>
       </c>
       <c r="J151" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K151" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="n">
         <v>84.3</v>
       </c>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="n">
+        <v>70.40000000000001</v>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P151" t="n">
-        <v>-10.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="152">
@@ -9244,34 +9018,38 @@
         <v>6</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Snow Day</t>
+          <t>Zoulette (IRE)</t>
         </is>
       </c>
       <c r="I152" t="n">
         <v>3</v>
       </c>
       <c r="J152" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K152" t="n">
-        <v>46</v>
-      </c>
-      <c r="L152" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
       <c r="M152" t="n">
         <v>84.3</v>
       </c>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="n">
+        <v>71.5</v>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>-10.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -9300,28 +9078,30 @@
         <v>6</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Escape Magic</t>
+          <t>Hatamoto</t>
         </is>
       </c>
       <c r="I153" t="n">
         <v>3</v>
       </c>
       <c r="J153" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K153" t="n">
-        <v>49</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="L153" t="n">
+        <v>3.25</v>
+      </c>
       <c r="M153" t="n">
         <v>84.3</v>
       </c>
       <c r="N153" t="n">
-        <v>70.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -9329,7 +9109,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -9358,30 +9138,30 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Zoulette (IRE)</t>
+          <t>Girls Allowed (IRE)</t>
         </is>
       </c>
       <c r="I154" t="n">
         <v>3</v>
       </c>
       <c r="J154" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K154" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="M154" t="n">
         <v>84.3</v>
       </c>
       <c r="N154" t="n">
-        <v>71.5</v>
+        <v>57.9</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -9389,7 +9169,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="155">
@@ -9418,30 +9198,30 @@
         <v>6</v>
       </c>
       <c r="G155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Hatamoto</t>
+          <t>Woody Y Fernandez</t>
         </is>
       </c>
       <c r="I155" t="n">
         <v>3</v>
       </c>
       <c r="J155" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K155" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L155" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="M155" t="n">
         <v>84.3</v>
       </c>
       <c r="N155" t="n">
-        <v>65.40000000000001</v>
+        <v>57.4</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -9449,7 +9229,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="156">
@@ -9478,30 +9258,30 @@
         <v>6</v>
       </c>
       <c r="G156" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Girls Allowed (IRE)</t>
+          <t>Giles Glory (IRE)</t>
         </is>
       </c>
       <c r="I156" t="n">
         <v>3</v>
       </c>
       <c r="J156" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K156" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L156" t="n">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="M156" t="n">
         <v>84.3</v>
       </c>
       <c r="N156" t="n">
-        <v>57.9</v>
+        <v>59.1</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -9509,7 +9289,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -9538,30 +9318,30 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Woody Y Fernandez</t>
+          <t>Telling Time</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>3</v>
       </c>
       <c r="J157" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K157" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L157" t="n">
-        <v>3.9</v>
+        <v>8.9</v>
       </c>
       <c r="M157" t="n">
         <v>84.3</v>
       </c>
       <c r="N157" t="n">
-        <v>57.4</v>
+        <v>45.3</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -9569,7 +9349,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -9598,30 +9378,30 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Giles Glory (IRE)</t>
+          <t>Shes Crafty (IRE)</t>
         </is>
       </c>
       <c r="I158" t="n">
         <v>3</v>
       </c>
       <c r="J158" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K158" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L158" t="n">
-        <v>4.65</v>
+        <v>12.65</v>
       </c>
       <c r="M158" t="n">
         <v>84.3</v>
       </c>
       <c r="N158" t="n">
-        <v>59.1</v>
+        <v>37.3</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -9629,7 +9409,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -9658,34 +9438,34 @@
         <v>6</v>
       </c>
       <c r="G159" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Telling Time</t>
+          <t>Muvable</t>
         </is>
       </c>
       <c r="I159" t="n">
         <v>3</v>
       </c>
       <c r="J159" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K159" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L159" t="n">
-        <v>8.9</v>
+        <v>22.15</v>
       </c>
       <c r="M159" t="n">
         <v>84.3</v>
       </c>
       <c r="N159" t="n">
-        <v>45.3</v>
+        <v>17.5</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -9717,40 +9497,24 @@
       <c r="F160" t="n">
         <v>6</v>
       </c>
-      <c r="G160" t="n">
-        <v>8</v>
-      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Shes Crafty (IRE)</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
-        <v>3</v>
-      </c>
-      <c r="J160" t="n">
-        <v>134</v>
-      </c>
-      <c r="K160" t="n">
-        <v>54</v>
-      </c>
-      <c r="L160" t="n">
-        <v>12.65</v>
-      </c>
-      <c r="M160" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="N160" t="n">
-        <v>37.3</v>
-      </c>
+          <t>Snow Day</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9777,40 +9541,24 @@
       <c r="F161" t="n">
         <v>6</v>
       </c>
-      <c r="G161" t="n">
-        <v>9</v>
-      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Muvable</t>
-        </is>
-      </c>
-      <c r="I161" t="n">
-        <v>3</v>
-      </c>
-      <c r="J161" t="n">
-        <v>126</v>
-      </c>
-      <c r="K161" t="n">
-        <v>46</v>
-      </c>
-      <c r="L161" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="M161" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="N161" t="n">
-        <v>17.5</v>
-      </c>
+          <t>Elashgar (IRE)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9838,34 +9586,36 @@
         <v>6</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Charencey (IRE)</t>
+          <t>Study Up</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K162" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="n">
         <v>126.77</v>
       </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>68.3</v>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -9894,28 +9644,30 @@
         <v>6</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Study Up</t>
+          <t>Happy Chandler</t>
         </is>
       </c>
       <c r="I163" t="n">
         <v>5</v>
       </c>
       <c r="J163" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K163" t="n">
-        <v>60</v>
-      </c>
-      <c r="L163" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M163" t="n">
         <v>126.77</v>
       </c>
       <c r="N163" t="n">
-        <v>68.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -9952,30 +9704,30 @@
         <v>6</v>
       </c>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Happy Chandler</t>
+          <t>Cartwheel</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J164" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K164" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L164" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="M164" t="n">
         <v>126.77</v>
       </c>
       <c r="N164" t="n">
-        <v>64.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -10012,30 +9764,30 @@
         <v>6</v>
       </c>
       <c r="G165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Cartwheel</t>
+          <t>Myna (IRE)</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J165" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="K165" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L165" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M165" t="n">
         <v>126.77</v>
       </c>
       <c r="N165" t="n">
-        <v>63</v>
+        <v>53.9</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -10072,30 +9824,30 @@
         <v>6</v>
       </c>
       <c r="G166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Myna (IRE)</t>
+          <t>Beauty Generation (IRE)</t>
         </is>
       </c>
       <c r="I166" t="n">
         <v>5</v>
       </c>
       <c r="J166" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="K166" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L166" t="n">
-        <v>2.6</v>
+        <v>6.35</v>
       </c>
       <c r="M166" t="n">
         <v>126.77</v>
       </c>
       <c r="N166" t="n">
-        <v>53.9</v>
+        <v>52.7</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -10132,15 +9884,15 @@
         <v>6</v>
       </c>
       <c r="G167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Beauty Generation (IRE)</t>
+          <t>Staffordshire (IRE)</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J167" t="n">
         <v>132</v>
@@ -10149,13 +9901,13 @@
         <v>57</v>
       </c>
       <c r="L167" t="n">
-        <v>6.35</v>
+        <v>9.1</v>
       </c>
       <c r="M167" t="n">
         <v>126.77</v>
       </c>
       <c r="N167" t="n">
-        <v>52.7</v>
+        <v>49.1</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -10192,30 +9944,30 @@
         <v>6</v>
       </c>
       <c r="G168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Staffordshire (IRE)</t>
+          <t>San Francisco Bay (IRE)</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J168" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K168" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L168" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="M168" t="n">
         <v>126.77</v>
       </c>
       <c r="N168" t="n">
-        <v>49.1</v>
+        <v>47.5</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -10252,30 +10004,30 @@
         <v>6</v>
       </c>
       <c r="G169" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>San Francisco Bay (IRE)</t>
+          <t>Ottoman (IRE)</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J169" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K169" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L169" t="n">
-        <v>9.6</v>
+        <v>10.85</v>
       </c>
       <c r="M169" t="n">
         <v>126.77</v>
       </c>
       <c r="N169" t="n">
-        <v>47.5</v>
+        <v>41.7</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -10311,40 +10063,24 @@
       <c r="F170" t="n">
         <v>6</v>
       </c>
-      <c r="G170" t="n">
-        <v>8</v>
-      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Ottoman (IRE)</t>
-        </is>
-      </c>
-      <c r="I170" t="n">
-        <v>4</v>
-      </c>
-      <c r="J170" t="n">
-        <v>130</v>
-      </c>
-      <c r="K170" t="n">
-        <v>55</v>
-      </c>
-      <c r="L170" t="n">
-        <v>10.85</v>
-      </c>
-      <c r="M170" t="n">
-        <v>126.77</v>
-      </c>
-      <c r="N170" t="n">
-        <v>41.7</v>
-      </c>
+          <t>Charencey (IRE)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
+      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10372,34 +10108,36 @@
         <v>5</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Perineighs (IRE)</t>
+          <t>Polka Blue (IRE)</t>
         </is>
       </c>
       <c r="I171" t="n">
         <v>3</v>
       </c>
       <c r="J171" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K171" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="n">
         <v>70.3</v>
       </c>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" t="n">
+        <v>80.2</v>
+      </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>-9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -10428,34 +10166,38 @@
         <v>5</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Nebbia</t>
+          <t>Frantic</t>
         </is>
       </c>
       <c r="I172" t="n">
         <v>3</v>
       </c>
       <c r="J172" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K172" t="n">
-        <v>67</v>
-      </c>
-      <c r="L172" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M172" t="n">
         <v>70.3</v>
       </c>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="n">
+        <v>76.8</v>
+      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>-9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -10484,28 +10226,30 @@
         <v>5</v>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Polka Blue (IRE)</t>
+          <t>Always Perfect (IRE)</t>
         </is>
       </c>
       <c r="I173" t="n">
         <v>3</v>
       </c>
       <c r="J173" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K173" t="n">
-        <v>68</v>
-      </c>
-      <c r="L173" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M173" t="n">
         <v>70.3</v>
       </c>
       <c r="N173" t="n">
-        <v>80.2</v>
+        <v>69.3</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -10542,30 +10286,30 @@
         <v>5</v>
       </c>
       <c r="G174" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Frantic</t>
+          <t>Anorah Unleashed (IRE)</t>
         </is>
       </c>
       <c r="I174" t="n">
         <v>3</v>
       </c>
       <c r="J174" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="K174" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="L174" t="n">
-        <v>1.25</v>
+        <v>7.25</v>
       </c>
       <c r="M174" t="n">
         <v>70.3</v>
       </c>
       <c r="N174" t="n">
-        <v>76.8</v>
+        <v>48.1</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -10573,7 +10317,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="175">
@@ -10602,30 +10346,30 @@
         <v>5</v>
       </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Always Perfect (IRE)</t>
+          <t>Blindfold Games (IRE)</t>
         </is>
       </c>
       <c r="I175" t="n">
         <v>3</v>
       </c>
       <c r="J175" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K175" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L175" t="n">
-        <v>1.75</v>
+        <v>8.5</v>
       </c>
       <c r="M175" t="n">
         <v>70.3</v>
       </c>
       <c r="N175" t="n">
-        <v>69.3</v>
+        <v>49.3</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -10633,7 +10377,7 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -10662,30 +10406,30 @@
         <v>5</v>
       </c>
       <c r="G176" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Anorah Unleashed (IRE)</t>
+          <t>Hewi</t>
         </is>
       </c>
       <c r="I176" t="n">
         <v>3</v>
       </c>
       <c r="J176" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K176" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="L176" t="n">
-        <v>7.25</v>
+        <v>10</v>
       </c>
       <c r="M176" t="n">
         <v>70.3</v>
       </c>
       <c r="N176" t="n">
-        <v>48.1</v>
+        <v>46.1</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -10693,7 +10437,7 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -10722,30 +10466,30 @@
         <v>5</v>
       </c>
       <c r="G177" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Blindfold Games (IRE)</t>
+          <t>Filly Foden (IRE)</t>
         </is>
       </c>
       <c r="I177" t="n">
         <v>3</v>
       </c>
       <c r="J177" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K177" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L177" t="n">
-        <v>8.5</v>
+        <v>10.05</v>
       </c>
       <c r="M177" t="n">
         <v>70.3</v>
       </c>
       <c r="N177" t="n">
-        <v>49.3</v>
+        <v>42.8</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -10753,7 +10497,7 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -10782,34 +10526,34 @@
         <v>5</v>
       </c>
       <c r="G178" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Hewi</t>
+          <t>Yasalam</t>
         </is>
       </c>
       <c r="I178" t="n">
         <v>3</v>
       </c>
       <c r="J178" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="K178" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L178" t="n">
-        <v>10</v>
+        <v>21.05</v>
       </c>
       <c r="M178" t="n">
         <v>70.3</v>
       </c>
       <c r="N178" t="n">
-        <v>46.1</v>
+        <v>29.2</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -10841,40 +10585,24 @@
       <c r="F179" t="n">
         <v>5</v>
       </c>
-      <c r="G179" t="n">
-        <v>7</v>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Filly Foden (IRE)</t>
-        </is>
-      </c>
-      <c r="I179" t="n">
-        <v>3</v>
-      </c>
-      <c r="J179" t="n">
-        <v>129</v>
-      </c>
-      <c r="K179" t="n">
-        <v>64</v>
-      </c>
-      <c r="L179" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="M179" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="N179" t="n">
-        <v>42.8</v>
-      </c>
+          <t>Nebbia</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P179" t="n">
-        <v>0</v>
-      </c>
+      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10901,40 +10629,24 @@
       <c r="F180" t="n">
         <v>5</v>
       </c>
-      <c r="G180" t="n">
-        <v>8</v>
-      </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Yasalam</t>
-        </is>
-      </c>
-      <c r="I180" t="n">
-        <v>3</v>
-      </c>
-      <c r="J180" t="n">
-        <v>134</v>
-      </c>
-      <c r="K180" t="n">
-        <v>69</v>
-      </c>
-      <c r="L180" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="M180" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="N180" t="n">
-        <v>29.2</v>
-      </c>
+          <t>Perineighs (IRE)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P180" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11260,34 +10972,36 @@
         <v>4</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Across Earth (IRE)</t>
+          <t>Synergism (GER)</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J186" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K186" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="n">
         <v>185.99</v>
       </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="n">
+        <v>56.7</v>
+      </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -11316,28 +11030,30 @@
         <v>4</v>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Synergism (GER)</t>
+          <t>Macari</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J187" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="K187" t="n">
-        <v>87</v>
-      </c>
-      <c r="L187" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M187" t="n">
         <v>185.99</v>
       </c>
       <c r="N187" t="n">
-        <v>56.7</v>
+        <v>45.9</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -11374,30 +11090,30 @@
         <v>4</v>
       </c>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Macari</t>
+          <t>Russian Rumour (IRE)</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J188" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="K188" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L188" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M188" t="n">
         <v>185.99</v>
       </c>
       <c r="N188" t="n">
-        <v>51.5</v>
+        <v>39.8</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -11434,30 +11150,30 @@
         <v>4</v>
       </c>
       <c r="G189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Russian Rumour (IRE)</t>
+          <t>Youthful King</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J189" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K189" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L189" t="n">
-        <v>1.5</v>
+        <v>4.25</v>
       </c>
       <c r="M189" t="n">
         <v>185.99</v>
       </c>
       <c r="N189" t="n">
-        <v>45.9</v>
+        <v>38.9</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -11493,40 +11209,24 @@
       <c r="F190" t="n">
         <v>4</v>
       </c>
-      <c r="G190" t="n">
-        <v>4</v>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Youthful King</t>
-        </is>
-      </c>
-      <c r="I190" t="n">
-        <v>7</v>
-      </c>
-      <c r="J190" t="n">
-        <v>131</v>
-      </c>
-      <c r="K190" t="n">
-        <v>81</v>
-      </c>
-      <c r="L190" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="M190" t="n">
-        <v>185.99</v>
-      </c>
-      <c r="N190" t="n">
-        <v>44</v>
-      </c>
+          <t>Across Earth (IRE)</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11554,11 +11254,11 @@
         <v>3</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Sunshine Star</t>
+          <t>Bintknight</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -11574,14 +11274,16 @@
       <c r="M191" t="n">
         <v>128</v>
       </c>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="n">
+        <v>74.09999999999999</v>
+      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -11610,11 +11312,11 @@
         <v>3</v>
       </c>
       <c r="G192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Bintknight</t>
+          <t>Asset (GER)</t>
         </is>
       </c>
       <c r="I192" t="n">
@@ -11626,12 +11328,14 @@
       <c r="K192" t="n">
         <v>0</v>
       </c>
-      <c r="L192" t="inlineStr"/>
+      <c r="L192" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M192" t="n">
         <v>128</v>
       </c>
       <c r="N192" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -11668,11 +11372,11 @@
         <v>3</v>
       </c>
       <c r="G193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Asset (GER)</t>
+          <t>Green Area</t>
         </is>
       </c>
       <c r="I193" t="n">
@@ -11685,13 +11389,13 @@
         <v>0</v>
       </c>
       <c r="L193" t="n">
-        <v>0.15</v>
+        <v>4.15</v>
       </c>
       <c r="M193" t="n">
         <v>128</v>
       </c>
       <c r="N193" t="n">
-        <v>72.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -11728,30 +11432,30 @@
         <v>3</v>
       </c>
       <c r="G194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Green Area</t>
+          <t>Scarlet Letter (IRE)</t>
         </is>
       </c>
       <c r="I194" t="n">
         <v>3</v>
       </c>
       <c r="J194" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>4.15</v>
+        <v>6.9</v>
       </c>
       <c r="M194" t="n">
         <v>128</v>
       </c>
       <c r="N194" t="n">
-        <v>65.09999999999999</v>
+        <v>53.5</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -11787,40 +11491,24 @@
       <c r="F195" t="n">
         <v>3</v>
       </c>
-      <c r="G195" t="n">
-        <v>4</v>
-      </c>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Scarlet Letter (IRE)</t>
-        </is>
-      </c>
-      <c r="I195" t="n">
-        <v>3</v>
-      </c>
-      <c r="J195" t="n">
-        <v>128</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M195" t="n">
-        <v>128</v>
-      </c>
-      <c r="N195" t="n">
-        <v>58.3</v>
-      </c>
+          <t>Sunshine Star</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P195" t="n">
-        <v>0</v>
-      </c>
+      <c r="P195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11859,7 +11547,7 @@
         <v>3</v>
       </c>
       <c r="J196" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K196" t="n">
         <v>49</v>
@@ -11869,7 +11557,7 @@
         <v>70.63</v>
       </c>
       <c r="N196" t="n">
-        <v>79.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -11877,7 +11565,7 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197">
@@ -11937,7 +11625,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -11977,7 +11665,7 @@
         <v>3</v>
       </c>
       <c r="J198" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K198" t="n">
         <v>46</v>
@@ -11989,7 +11677,7 @@
         <v>70.63</v>
       </c>
       <c r="N198" t="n">
-        <v>71.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -11997,7 +11685,7 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="199">
@@ -12037,7 +11725,7 @@
         <v>3</v>
       </c>
       <c r="J199" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K199" t="n">
         <v>49</v>
@@ -12049,7 +11737,7 @@
         <v>70.63</v>
       </c>
       <c r="N199" t="n">
-        <v>71.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -12057,7 +11745,7 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="200">
@@ -12117,7 +11805,7 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -12177,7 +11865,7 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -12283,7 +11971,7 @@
         <v>47</v>
       </c>
       <c r="L203" t="n">
-        <v>5.18</v>
+        <v>5.180000000000001</v>
       </c>
       <c r="M203" t="n">
         <v>70.63</v>
@@ -12517,7 +12205,7 @@
         <v>3</v>
       </c>
       <c r="J207" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K207" t="n">
         <v>46</v>
@@ -12529,7 +12217,7 @@
         <v>70.63</v>
       </c>
       <c r="N207" t="n">
-        <v>54.3</v>
+        <v>48.5</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -12577,19 +12265,19 @@
         <v>3</v>
       </c>
       <c r="J208" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K208" t="n">
         <v>55</v>
       </c>
       <c r="L208" t="n">
-        <v>8.279999999999999</v>
+        <v>8.280000000000001</v>
       </c>
       <c r="M208" t="n">
         <v>70.63</v>
       </c>
       <c r="N208" t="n">
-        <v>59.1</v>
+        <v>56.4</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -12626,11 +12314,11 @@
         <v>4</v>
       </c>
       <c r="G209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Storming Point</t>
+          <t>Ascending Star (IRE)</t>
         </is>
       </c>
       <c r="I209" t="n">
@@ -12646,14 +12334,16 @@
       <c r="M209" t="n">
         <v>90.08</v>
       </c>
-      <c r="N209" t="inlineStr"/>
+      <c r="N209" t="n">
+        <v>82.3</v>
+      </c>
       <c r="O209" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P209" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -12682,11 +12372,11 @@
         <v>4</v>
       </c>
       <c r="G210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Ascending Star (IRE)</t>
+          <t>Weffaag</t>
         </is>
       </c>
       <c r="I210" t="n">
@@ -12698,12 +12388,14 @@
       <c r="K210" t="n">
         <v>0</v>
       </c>
-      <c r="L210" t="inlineStr"/>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
       <c r="M210" t="n">
         <v>90.08</v>
       </c>
       <c r="N210" t="n">
-        <v>82.3</v>
+        <v>79.5</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -12740,30 +12432,30 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Weffaag</t>
+          <t>Cosmic Girl</t>
         </is>
       </c>
       <c r="I211" t="n">
         <v>3</v>
       </c>
       <c r="J211" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="M211" t="n">
         <v>90.08</v>
       </c>
       <c r="N211" t="n">
-        <v>79.5</v>
+        <v>63.7</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -12800,30 +12492,30 @@
         <v>4</v>
       </c>
       <c r="G212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Cosmic Girl</t>
+          <t>Cormorant Rock (IRE)</t>
         </is>
       </c>
       <c r="I212" t="n">
         <v>3</v>
       </c>
       <c r="J212" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
       <c r="M212" t="n">
         <v>90.08</v>
       </c>
       <c r="N212" t="n">
-        <v>63.7</v>
+        <v>44.2</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -12860,11 +12552,11 @@
         <v>4</v>
       </c>
       <c r="G213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Cormorant Rock (IRE)</t>
+          <t>Blazing Sam</t>
         </is>
       </c>
       <c r="I213" t="n">
@@ -12877,17 +12569,17 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>15.5</v>
+        <v>28.5</v>
       </c>
       <c r="M213" t="n">
         <v>90.08</v>
       </c>
       <c r="N213" t="n">
-        <v>44.2</v>
+        <v>41.9</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -12919,40 +12611,24 @@
       <c r="F214" t="n">
         <v>4</v>
       </c>
-      <c r="G214" t="n">
-        <v>5</v>
-      </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Blazing Sam</t>
-        </is>
-      </c>
-      <c r="I214" t="n">
-        <v>3</v>
-      </c>
-      <c r="J214" t="n">
-        <v>133</v>
-      </c>
-      <c r="K214" t="n">
-        <v>0</v>
-      </c>
-      <c r="L214" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="M214" t="n">
-        <v>90.08</v>
-      </c>
-      <c r="N214" t="n">
-        <v>41.9</v>
-      </c>
+          <t>Storming Point</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P214" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12980,34 +12656,36 @@
         <v>5</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Eazy On The Eye</t>
+          <t>Summer Heat</t>
         </is>
       </c>
       <c r="I215" t="n">
         <v>4</v>
       </c>
       <c r="J215" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K215" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="n">
         <v>82.81999999999999</v>
       </c>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" t="n">
+        <v>76.5</v>
+      </c>
       <c r="O215" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P215" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -13036,28 +12714,30 @@
         <v>5</v>
       </c>
       <c r="G216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Summer Heat</t>
+          <t>Land Of Magic</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J216" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K216" t="n">
-        <v>72</v>
-      </c>
-      <c r="L216" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M216" t="n">
         <v>82.81999999999999</v>
       </c>
       <c r="N216" t="n">
-        <v>76.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -13065,7 +12745,7 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="217">
@@ -13094,30 +12774,30 @@
         <v>5</v>
       </c>
       <c r="G217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Land Of Magic</t>
+          <t>Hilltop</t>
         </is>
       </c>
       <c r="I217" t="n">
         <v>5</v>
       </c>
       <c r="J217" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K217" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L217" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="M217" t="n">
         <v>82.81999999999999</v>
       </c>
       <c r="N217" t="n">
-        <v>69.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -13125,7 +12805,7 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -13154,30 +12834,30 @@
         <v>5</v>
       </c>
       <c r="G218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Hilltop</t>
+          <t>Bella Bisbee</t>
         </is>
       </c>
       <c r="I218" t="n">
         <v>5</v>
       </c>
       <c r="J218" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K218" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L218" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="M218" t="n">
         <v>82.81999999999999</v>
       </c>
       <c r="N218" t="n">
-        <v>75.5</v>
+        <v>66.3</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -13185,7 +12865,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -13214,30 +12894,30 @@
         <v>5</v>
       </c>
       <c r="G219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Bella Bisbee</t>
+          <t>Welljudged</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J219" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K219" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L219" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="M219" t="n">
         <v>82.81999999999999</v>
       </c>
       <c r="N219" t="n">
-        <v>66.3</v>
+        <v>49.2</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -13245,7 +12925,7 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="220">
@@ -13274,30 +12954,30 @@
         <v>5</v>
       </c>
       <c r="G220" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Welljudged</t>
+          <t>Thunderous Love</t>
         </is>
       </c>
       <c r="I220" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J220" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K220" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L220" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="M220" t="n">
         <v>82.81999999999999</v>
       </c>
       <c r="N220" t="n">
-        <v>52.2</v>
+        <v>49.6</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -13305,7 +12985,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -13334,30 +13014,30 @@
         <v>5</v>
       </c>
       <c r="G221" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Thunderous Love</t>
+          <t>Daisy Roots</t>
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J221" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K221" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L221" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="M221" t="n">
         <v>82.81999999999999</v>
       </c>
       <c r="N221" t="n">
-        <v>49.6</v>
+        <v>37.5</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -13393,40 +13073,24 @@
       <c r="F222" t="n">
         <v>5</v>
       </c>
-      <c r="G222" t="n">
-        <v>7</v>
-      </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Daisy Roots</t>
-        </is>
-      </c>
-      <c r="I222" t="n">
-        <v>6</v>
-      </c>
-      <c r="J222" t="n">
-        <v>129</v>
-      </c>
-      <c r="K222" t="n">
-        <v>69</v>
-      </c>
-      <c r="L222" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M222" t="n">
-        <v>82.81999999999999</v>
-      </c>
-      <c r="N222" t="n">
-        <v>37.5</v>
-      </c>
+          <t>Eazy On The Eye</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P222" t="n">
-        <v>0</v>
-      </c>
+      <c r="P222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13454,11 +13118,11 @@
         <v>5</v>
       </c>
       <c r="G223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Kimbara</t>
+          <t>Mighty Vega (IRE)</t>
         </is>
       </c>
       <c r="I223" t="n">
@@ -13474,14 +13138,16 @@
       <c r="M223" t="n">
         <v>82.64</v>
       </c>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" t="n">
+        <v>84.59999999999999</v>
+      </c>
       <c r="O223" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P223" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -13510,28 +13176,30 @@
         <v>5</v>
       </c>
       <c r="G224" t="n">
+        <v>2</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Lohoobb</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>3</v>
+      </c>
+      <c r="J224" t="n">
+        <v>135</v>
+      </c>
+      <c r="K224" t="n">
+        <v>75</v>
+      </c>
+      <c r="L224" t="n">
         <v>1</v>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Mighty Vega (IRE)</t>
-        </is>
-      </c>
-      <c r="I224" t="n">
-        <v>3</v>
-      </c>
-      <c r="J224" t="n">
-        <v>132</v>
-      </c>
-      <c r="K224" t="n">
-        <v>72</v>
-      </c>
-      <c r="L224" t="inlineStr"/>
       <c r="M224" t="n">
         <v>82.64</v>
       </c>
       <c r="N224" t="n">
-        <v>84.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -13568,30 +13236,30 @@
         <v>5</v>
       </c>
       <c r="G225" t="n">
+        <v>3</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Luminare (IRE)</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>3</v>
+      </c>
+      <c r="J225" t="n">
+        <v>134</v>
+      </c>
+      <c r="K225" t="n">
+        <v>74</v>
+      </c>
+      <c r="L225" t="n">
         <v>2</v>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Lohoobb</t>
-        </is>
-      </c>
-      <c r="I225" t="n">
-        <v>3</v>
-      </c>
-      <c r="J225" t="n">
-        <v>135</v>
-      </c>
-      <c r="K225" t="n">
-        <v>75</v>
-      </c>
-      <c r="L225" t="n">
-        <v>1</v>
       </c>
       <c r="M225" t="n">
         <v>82.64</v>
       </c>
       <c r="N225" t="n">
-        <v>83.2</v>
+        <v>78.5</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -13628,11 +13296,11 @@
         <v>5</v>
       </c>
       <c r="G226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Luminare (IRE)</t>
+          <t>High Approval (IRE)</t>
         </is>
       </c>
       <c r="I226" t="n">
@@ -13645,13 +13313,13 @@
         <v>74</v>
       </c>
       <c r="L226" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="M226" t="n">
         <v>82.64</v>
       </c>
       <c r="N226" t="n">
-        <v>78.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -13688,30 +13356,30 @@
         <v>5</v>
       </c>
       <c r="G227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>High Approval (IRE)</t>
+          <t>Torbados</t>
         </is>
       </c>
       <c r="I227" t="n">
         <v>3</v>
       </c>
       <c r="J227" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="K227" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L227" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="M227" t="n">
         <v>82.64</v>
       </c>
       <c r="N227" t="n">
-        <v>72.40000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -13748,30 +13416,30 @@
         <v>5</v>
       </c>
       <c r="G228" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Torbados</t>
+          <t>Venetian Romance (IRE)</t>
         </is>
       </c>
       <c r="I228" t="n">
         <v>3</v>
       </c>
       <c r="J228" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K228" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L228" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="M228" t="n">
         <v>82.64</v>
       </c>
       <c r="N228" t="n">
-        <v>63.8</v>
+        <v>59.3</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -13808,30 +13476,30 @@
         <v>5</v>
       </c>
       <c r="G229" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Venetian Romance (IRE)</t>
+          <t>Victor Cee</t>
         </is>
       </c>
       <c r="I229" t="n">
         <v>3</v>
       </c>
       <c r="J229" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K229" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L229" t="n">
-        <v>5.15</v>
+        <v>16.15</v>
       </c>
       <c r="M229" t="n">
         <v>82.64</v>
       </c>
       <c r="N229" t="n">
-        <v>62.1</v>
+        <v>34.9</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -13867,40 +13535,24 @@
       <c r="F230" t="n">
         <v>5</v>
       </c>
-      <c r="G230" t="n">
-        <v>7</v>
-      </c>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Victor Cee</t>
-        </is>
-      </c>
-      <c r="I230" t="n">
-        <v>3</v>
-      </c>
-      <c r="J230" t="n">
-        <v>130</v>
-      </c>
-      <c r="K230" t="n">
-        <v>70</v>
-      </c>
-      <c r="L230" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="M230" t="n">
-        <v>82.64</v>
-      </c>
-      <c r="N230" t="n">
-        <v>34.9</v>
-      </c>
+          <t>Kimbara</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P230" t="n">
-        <v>0</v>
-      </c>
+      <c r="P230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15429,7 +15081,7 @@
         <v>3</v>
       </c>
       <c r="J256" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K256" t="n">
         <v>64</v>
@@ -15441,7 +15093,7 @@
         <v>83.41</v>
       </c>
       <c r="N256" t="n">
-        <v>77.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -15569,7 +15221,7 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="259">
@@ -15689,7 +15341,7 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="261">
@@ -15729,7 +15381,7 @@
         <v>3</v>
       </c>
       <c r="J261" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K261" t="n">
         <v>62</v>
@@ -15741,7 +15393,7 @@
         <v>83.41</v>
       </c>
       <c r="N261" t="n">
-        <v>62.7</v>
+        <v>55.6</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -15749,7 +15401,7 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="262">
@@ -15809,7 +15461,7 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="263">
@@ -15869,7 +15521,7 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
@@ -15929,7 +15581,7 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265">
@@ -15969,7 +15621,7 @@
         <v>3</v>
       </c>
       <c r="J265" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K265" t="n">
         <v>64</v>
@@ -15981,7 +15633,7 @@
         <v>83.41</v>
       </c>
       <c r="N265" t="n">
-        <v>54.7</v>
+        <v>50.5</v>
       </c>
       <c r="O265" t="inlineStr">
         <is>
@@ -15989,7 +15641,7 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -16149,7 +15801,7 @@
         <v>5</v>
       </c>
       <c r="J268" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K268" t="n">
         <v>52</v>
@@ -16159,7 +15811,7 @@
         <v>58.07</v>
       </c>
       <c r="N268" t="n">
-        <v>72.8</v>
+        <v>70</v>
       </c>
       <c r="O268" t="inlineStr">
         <is>
@@ -16387,7 +16039,7 @@
         <v>7</v>
       </c>
       <c r="J272" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K272" t="n">
         <v>54</v>
@@ -16399,7 +16051,7 @@
         <v>58.07</v>
       </c>
       <c r="N272" t="n">
-        <v>59.9</v>
+        <v>58.2</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -16747,7 +16399,7 @@
         <v>4</v>
       </c>
       <c r="J278" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K278" t="n">
         <v>58</v>
@@ -16757,7 +16409,7 @@
         <v>70.88</v>
       </c>
       <c r="N278" t="n">
-        <v>80.8</v>
+        <v>78.3</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -16865,7 +16517,7 @@
         <v>6</v>
       </c>
       <c r="J280" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="K280" t="n">
         <v>60</v>
@@ -16877,7 +16529,7 @@
         <v>70.88</v>
       </c>
       <c r="N280" t="n">
-        <v>78.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -16985,7 +16637,7 @@
         <v>8</v>
       </c>
       <c r="J282" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K282" t="n">
         <v>55</v>
@@ -16997,7 +16649,7 @@
         <v>70.88</v>
       </c>
       <c r="N282" t="n">
-        <v>71.5</v>
+        <v>69.2</v>
       </c>
       <c r="O282" t="inlineStr">
         <is>
@@ -17045,7 +16697,7 @@
         <v>7</v>
       </c>
       <c r="J283" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K283" t="n">
         <v>58</v>
@@ -17057,7 +16709,7 @@
         <v>70.88</v>
       </c>
       <c r="N283" t="n">
-        <v>71.7</v>
+        <v>70.7</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -17165,7 +16817,7 @@
         <v>6</v>
       </c>
       <c r="J285" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="K285" t="n">
         <v>53</v>
@@ -17177,7 +16829,7 @@
         <v>70.88</v>
       </c>
       <c r="N285" t="n">
-        <v>58.5</v>
+        <v>57</v>
       </c>
       <c r="O285" t="inlineStr">
         <is>
@@ -17225,7 +16877,7 @@
         <v>9</v>
       </c>
       <c r="J286" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="K286" t="n">
         <v>46</v>
@@ -17237,7 +16889,7 @@
         <v>70.88</v>
       </c>
       <c r="N286" t="n">
-        <v>53.4</v>
+        <v>48.4</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -17245,7 +16897,7 @@
         </is>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="287">
@@ -17285,19 +16937,19 @@
         <v>5</v>
       </c>
       <c r="J287" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K287" t="n">
         <v>46</v>
       </c>
       <c r="L287" t="n">
-        <v>6.949999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="M287" t="n">
         <v>70.88</v>
       </c>
       <c r="N287" t="n">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="O287" t="inlineStr">
         <is>
@@ -17305,7 +16957,7 @@
         </is>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -17405,7 +17057,7 @@
         <v>7</v>
       </c>
       <c r="J289" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K289" t="n">
         <v>52</v>
@@ -17417,7 +17069,7 @@
         <v>70.88</v>
       </c>
       <c r="N289" t="n">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
